--- a/RMUTL_WORK/Teaching work/2025/เทอม_02/ENGCE117_Computer Programming for Computer Engineer/SCORE_117.xlsx
+++ b/RMUTL_WORK/Teaching work/2025/เทอม_02/ENGCE117_Computer Programming for Computer Engineer/SCORE_117.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LOBSTER69\Documents\GitHub\WORK\RMUTL_WORK\Teaching work\2025\เทอม_02\ENGCE117_Computer Programming for Computer Engineer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LOBSTER69\Documents\WORK\RMUTL_WORK\Teaching work\2025\เทอม_02\ENGCE117_Computer Programming for Computer Engineer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7ECB9A-919A-4AF0-B98E-1662A4EC5B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A34C8CF-FB2B-426B-A913-AF126DAFF3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ประวัติการศึกษา" sheetId="1" r:id="rId1"/>
@@ -400,7 +400,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
@@ -703,29 +703,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R30"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="24" x14ac:dyDescent="0.8"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="24" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="7.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.7265625" style="1"/>
+    <col min="19" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -747,7 +747,7 @@
       <c r="Q1" s="18"/>
       <c r="R1" s="18"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="18" t="s">
         <v>62</v>
       </c>
@@ -769,7 +769,7 @@
       <c r="Q2" s="18"/>
       <c r="R2" s="18"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="18" t="s">
         <v>60</v>
       </c>
@@ -791,7 +791,7 @@
       <c r="Q3" s="18"/>
       <c r="R3" s="18"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="18" t="s">
         <v>1</v>
       </c>
@@ -813,7 +813,7 @@
       <c r="Q4" s="18"/>
       <c r="R4" s="18"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="19" t="s">
         <v>2</v>
       </c>
@@ -853,7 +853,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="19"/>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -873,7 +873,7 @@
       <c r="Q6" s="19"/>
       <c r="R6" s="19"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="19"/>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -913,7 +913,7 @@
       <c r="Q7" s="19"/>
       <c r="R7" s="19"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -944,21 +944,23 @@
       <c r="J8" s="9">
         <v>5</v>
       </c>
-      <c r="K8" s="9"/>
+      <c r="K8" s="9">
+        <v>3.1</v>
+      </c>
       <c r="L8" s="9"/>
       <c r="M8" s="9">
         <v>4</v>
       </c>
       <c r="N8" s="9">
         <f>SUM(D8:M8)</f>
-        <v>38.4</v>
+        <v>41.5</v>
       </c>
       <c r="O8" s="5"/>
       <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
       <c r="R8" s="10"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3">
         <v>2</v>
       </c>
@@ -989,21 +991,23 @@
       <c r="J9" s="9">
         <v>5</v>
       </c>
-      <c r="K9" s="9"/>
+      <c r="K9" s="9">
+        <v>2.2999999999999998</v>
+      </c>
       <c r="L9" s="9"/>
       <c r="M9" s="9">
         <v>3</v>
       </c>
       <c r="N9" s="9">
         <f>SUM(D9:M9)</f>
-        <v>32.480000000000004</v>
+        <v>34.78</v>
       </c>
       <c r="O9" s="5"/>
       <c r="P9" s="9"/>
       <c r="Q9" s="9"/>
       <c r="R9" s="10"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="3">
         <v>3</v>
       </c>
@@ -1034,21 +1038,23 @@
       <c r="J10" s="9">
         <v>5</v>
       </c>
-      <c r="K10" s="9"/>
+      <c r="K10" s="9">
+        <v>7.3</v>
+      </c>
       <c r="L10" s="9"/>
       <c r="M10" s="9">
         <v>5</v>
       </c>
       <c r="N10" s="9">
         <f>SUM(D10:M10)</f>
-        <v>45.7</v>
+        <v>53</v>
       </c>
       <c r="O10" s="9"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="9"/>
       <c r="R10" s="10"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -1076,7 +1082,7 @@
       <c r="Q11" s="16"/>
       <c r="R11" s="17"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="3">
         <v>5</v>
       </c>
@@ -1107,21 +1113,23 @@
       <c r="J12" s="9">
         <v>5</v>
       </c>
-      <c r="K12" s="9"/>
+      <c r="K12" s="9">
+        <v>4.5</v>
+      </c>
       <c r="L12" s="9"/>
       <c r="M12" s="9">
         <v>4</v>
       </c>
       <c r="N12" s="9">
         <f t="shared" ref="N12:N28" si="0">SUM(D12:M12)</f>
-        <v>28.7</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="O12" s="9"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="9"/>
       <c r="R12" s="10"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3">
         <v>6</v>
       </c>
@@ -1152,21 +1160,23 @@
       <c r="J13" s="9">
         <v>5</v>
       </c>
-      <c r="K13" s="9"/>
+      <c r="K13" s="9">
+        <v>2.5</v>
+      </c>
       <c r="L13" s="9"/>
       <c r="M13" s="9">
         <v>4</v>
       </c>
       <c r="N13" s="9">
         <f t="shared" si="0"/>
-        <v>25.04</v>
+        <v>27.54</v>
       </c>
       <c r="O13" s="9"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="9"/>
       <c r="R13" s="10"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -1197,21 +1207,23 @@
       <c r="J14" s="9">
         <v>5</v>
       </c>
-      <c r="K14" s="9"/>
+      <c r="K14" s="9">
+        <v>6.8</v>
+      </c>
       <c r="L14" s="9"/>
       <c r="M14" s="9">
         <v>5</v>
       </c>
       <c r="N14" s="9">
         <f t="shared" si="0"/>
-        <v>42.96</v>
+        <v>49.76</v>
       </c>
       <c r="O14" s="9"/>
       <c r="P14" s="9"/>
       <c r="Q14" s="9"/>
       <c r="R14" s="10"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="7">
         <v>8</v>
       </c>
@@ -1242,7 +1254,9 @@
       <c r="J15" s="11">
         <v>5</v>
       </c>
-      <c r="K15" s="11"/>
+      <c r="K15" s="11">
+        <v>0</v>
+      </c>
       <c r="L15" s="11"/>
       <c r="M15" s="11">
         <v>0</v>
@@ -1256,7 +1270,7 @@
       <c r="Q15" s="11"/>
       <c r="R15" s="12"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -1287,21 +1301,23 @@
       <c r="J16" s="9">
         <v>5</v>
       </c>
-      <c r="K16" s="9"/>
+      <c r="K16" s="9">
+        <v>3.5</v>
+      </c>
       <c r="L16" s="9"/>
       <c r="M16" s="9">
         <v>2</v>
       </c>
       <c r="N16" s="9">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>36</v>
       </c>
       <c r="O16" s="9"/>
       <c r="P16" s="9"/>
       <c r="Q16" s="9"/>
       <c r="R16" s="10"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -1332,21 +1348,23 @@
       <c r="J17" s="9">
         <v>5</v>
       </c>
-      <c r="K17" s="9"/>
+      <c r="K17" s="9">
+        <v>4.5</v>
+      </c>
       <c r="L17" s="9"/>
       <c r="M17" s="9">
         <v>5</v>
       </c>
       <c r="N17" s="9">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>42.5</v>
       </c>
       <c r="O17" s="9"/>
       <c r="P17" s="9"/>
       <c r="Q17" s="9"/>
       <c r="R17" s="10"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -1377,21 +1395,23 @@
       <c r="J18" s="9">
         <v>5</v>
       </c>
-      <c r="K18" s="9"/>
+      <c r="K18" s="9">
+        <v>7</v>
+      </c>
       <c r="L18" s="9"/>
       <c r="M18" s="9">
         <v>5</v>
       </c>
       <c r="N18" s="9">
         <f t="shared" si="0"/>
-        <v>49.7</v>
+        <v>56.7</v>
       </c>
       <c r="O18" s="13"/>
       <c r="P18" s="13"/>
       <c r="Q18" s="13"/>
       <c r="R18" s="13"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -1422,21 +1442,23 @@
       <c r="J19" s="14">
         <v>5</v>
       </c>
-      <c r="K19" s="14"/>
+      <c r="K19" s="14">
+        <v>4.5</v>
+      </c>
       <c r="L19" s="14"/>
       <c r="M19" s="9">
         <v>5</v>
       </c>
       <c r="N19" s="9">
         <f t="shared" si="0"/>
-        <v>39.980000000000004</v>
+        <v>44.480000000000004</v>
       </c>
       <c r="O19" s="13"/>
       <c r="P19" s="13"/>
       <c r="Q19" s="13"/>
       <c r="R19" s="13"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -1467,21 +1489,23 @@
       <c r="J20" s="14">
         <v>5</v>
       </c>
-      <c r="K20" s="14"/>
+      <c r="K20" s="14">
+        <v>7.1</v>
+      </c>
       <c r="L20" s="14"/>
       <c r="M20" s="14">
         <v>5</v>
       </c>
       <c r="N20" s="9">
         <f t="shared" si="0"/>
-        <v>50.1</v>
+        <v>57.2</v>
       </c>
       <c r="O20" s="13"/>
       <c r="P20" s="13"/>
       <c r="Q20" s="13"/>
       <c r="R20" s="13"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -1512,21 +1536,23 @@
       <c r="J21" s="14">
         <v>5</v>
       </c>
-      <c r="K21" s="14"/>
+      <c r="K21" s="14">
+        <v>4.5999999999999996</v>
+      </c>
       <c r="L21" s="14"/>
       <c r="M21" s="14">
         <v>5</v>
       </c>
       <c r="N21" s="9">
         <f>SUM(D21:M21)</f>
-        <v>39.799999999999997</v>
+        <v>44.4</v>
       </c>
       <c r="O21" s="13"/>
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
       <c r="R21" s="13"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -1557,21 +1583,23 @@
       <c r="J22" s="14">
         <v>5</v>
       </c>
-      <c r="K22" s="14"/>
+      <c r="K22" s="14">
+        <v>3.4</v>
+      </c>
       <c r="L22" s="14"/>
       <c r="M22" s="14">
         <v>5</v>
       </c>
       <c r="N22" s="9">
         <f t="shared" si="0"/>
-        <v>38.049999999999997</v>
+        <v>41.449999999999996</v>
       </c>
       <c r="O22" s="13"/>
       <c r="P22" s="13"/>
       <c r="Q22" s="13"/>
       <c r="R22" s="13"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3">
         <v>16</v>
       </c>
@@ -1602,21 +1630,23 @@
       <c r="J23" s="14">
         <v>5</v>
       </c>
-      <c r="K23" s="14"/>
+      <c r="K23" s="14">
+        <v>6.3</v>
+      </c>
       <c r="L23" s="14"/>
       <c r="M23" s="14">
         <v>4</v>
       </c>
       <c r="N23" s="9">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>56.3</v>
       </c>
       <c r="O23" s="13"/>
       <c r="P23" s="13"/>
       <c r="Q23" s="13"/>
       <c r="R23" s="13"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="3">
         <v>17</v>
       </c>
@@ -1647,21 +1677,23 @@
       <c r="J24" s="14">
         <v>5</v>
       </c>
-      <c r="K24" s="14"/>
+      <c r="K24" s="14">
+        <v>5.8</v>
+      </c>
       <c r="L24" s="14"/>
       <c r="M24" s="14">
         <v>5</v>
       </c>
       <c r="N24" s="9">
         <f t="shared" si="0"/>
-        <v>48.65</v>
+        <v>54.449999999999996</v>
       </c>
       <c r="O24" s="13"/>
       <c r="P24" s="13"/>
       <c r="Q24" s="13"/>
       <c r="R24" s="13"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="3">
         <v>18</v>
       </c>
@@ -1692,21 +1724,23 @@
       <c r="J25" s="14">
         <v>5</v>
       </c>
-      <c r="K25" s="14"/>
+      <c r="K25" s="14">
+        <v>6.4</v>
+      </c>
       <c r="L25" s="14"/>
       <c r="M25" s="14">
         <v>5</v>
       </c>
       <c r="N25" s="9">
         <f t="shared" si="0"/>
-        <v>43.95</v>
+        <v>50.35</v>
       </c>
       <c r="O25" s="13"/>
       <c r="P25" s="13"/>
       <c r="Q25" s="13"/>
       <c r="R25" s="13"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="3">
         <v>19</v>
       </c>
@@ -1737,21 +1771,23 @@
       <c r="J26" s="14">
         <v>5</v>
       </c>
-      <c r="K26" s="14"/>
+      <c r="K26" s="14">
+        <v>6.2</v>
+      </c>
       <c r="L26" s="14"/>
       <c r="M26" s="14">
         <v>5</v>
       </c>
       <c r="N26" s="9">
         <f t="shared" si="0"/>
-        <v>40.769999999999996</v>
+        <v>46.97</v>
       </c>
       <c r="O26" s="13"/>
       <c r="P26" s="13"/>
       <c r="Q26" s="13"/>
       <c r="R26" s="13"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="3">
         <v>20</v>
       </c>
@@ -1782,21 +1818,23 @@
       <c r="J27" s="14">
         <v>5</v>
       </c>
-      <c r="K27" s="14"/>
+      <c r="K27" s="14">
+        <v>6.9</v>
+      </c>
       <c r="L27" s="14"/>
       <c r="M27" s="14">
         <v>5</v>
       </c>
       <c r="N27" s="9">
         <f t="shared" si="0"/>
-        <v>47.35</v>
+        <v>54.25</v>
       </c>
       <c r="O27" s="13"/>
       <c r="P27" s="13"/>
       <c r="Q27" s="13"/>
       <c r="R27" s="13"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="3">
         <v>21</v>
       </c>
@@ -1827,7 +1865,9 @@
       <c r="J28" s="14">
         <v>5</v>
       </c>
-      <c r="K28" s="14"/>
+      <c r="K28" s="14">
+        <v>0</v>
+      </c>
       <c r="L28" s="14"/>
       <c r="M28" s="14">
         <v>2</v>
@@ -1841,22 +1881,22 @@
       <c r="Q28" s="13"/>
       <c r="R28" s="13"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="M29" s="4" t="s">
         <v>32</v>
       </c>
       <c r="N29" s="5">
         <f>AVERAGE(N8:N28)</f>
-        <v>38.936500000000002</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.8">
+        <v>43.5715</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="M30" s="3" t="s">
         <v>33</v>
       </c>
       <c r="N30" s="2">
         <f>_xlfn.STDEV.P(N8:N28)</f>
-        <v>8.6448431304448796</v>
+        <v>10.658580240820053</v>
       </c>
     </row>
   </sheetData>
